--- a/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_e_basneta_a_2018.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_e_basneta_a_2018.xlsx
@@ -84,7 +84,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 13:43</t>
+    <t xml:space="preserve">2026-09-24 00:34</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -591,7 +591,7 @@
         <v>0.2</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="9">
@@ -602,10 +602,10 @@
         <v>13</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="10">
@@ -616,10 +616,10 @@
         <v>13</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="11">
@@ -630,10 +630,10 @@
         <v>13</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="12">

--- a/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_e_basneta_a_2018.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_e_basneta_a_2018.xlsx
@@ -84,7 +84,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:34</t>
+    <t xml:space="preserve">2026-10-01 23:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_e_basneta_a_2018.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_e_basneta_a_2018.xlsx
@@ -84,7 +84,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:04</t>
+    <t xml:space="preserve">2026-10-05 19:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
